--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prasannainamdar/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Endurance\Mendewadi Project\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BBF530-E7D0-5142-B2DD-39C75F437680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24560" yWindow="2700" windowWidth="33820" windowHeight="19220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24560" yWindow="2700" windowWidth="33820" windowHeight="19220" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="a" sheetId="10" r:id="rId1"/>
@@ -39,14 +38,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
@@ -84,7 +83,7 @@
     <t>Plant :</t>
   </si>
   <si>
-    <t>Mindewadi</t>
+    <t>Mendewadi</t>
   </si>
   <si>
     <t>Test Department :</t>
@@ -185,10 +184,10 @@
 (ΔT &lt;= 1.5 ℃)</t>
   </si>
   <si>
-    <t>CH_DeltaV (mV)</t>
-  </si>
-  <si>
-    <t>DCH_DeltaV (mV)</t>
+    <t>Short CDC CH_DeltaV (mV)</t>
+  </si>
+  <si>
+    <t>Short CDC DCH_DeltaV (mV)</t>
   </si>
   <si>
     <t>Capacity (Ah)</t>
@@ -1504,8 +1503,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2766,240 +2765,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3014,6 +2779,246 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3022,12 +3027,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3039,9 +3038,9 @@
   <cellStyles count="5">
     <cellStyle name="Good" xfId="4" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 19" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 19" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="3"/>
   </cellStyles>
   <dxfs count="19">
     <dxf>
@@ -3247,6 +3246,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>109682</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1098125</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>260753</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2C537196-A876-75D6-6725-77A75CD162EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="375227" y="311727"/>
+          <a:ext cx="1940943" cy="503208"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3629,9 +3677,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2BDA19B-996D-4328-BF67-B0BE60AFFDDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Y31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="1" bestFit="1" customWidth="1"/>
@@ -3654,27 +3702,25 @@
     <col min="21" max="16384" width="7.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:25" ht="23" x14ac:dyDescent="0.2">
-      <c r="B2" s="113" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="129" t="s">
+    <row r="1" spans="2:25" ht="14.5" thickBot="1"/>
+    <row r="2" spans="2:25" ht="23">
+      <c r="B2" s="128"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="131"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="117"/>
       <c r="Q2" s="28" t="s">
         <v>1</v>
       </c>
@@ -3682,24 +3728,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="B3" s="115"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="132" t="s">
+    <row r="3" spans="2:25" ht="18">
+      <c r="B3" s="130"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="134"/>
-      <c r="M3" s="134"/>
-      <c r="N3" s="134"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="135"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="120"/>
+      <c r="O3" s="120"/>
+      <c r="P3" s="121"/>
       <c r="Q3" s="5" t="s">
         <v>4</v>
       </c>
@@ -3707,7 +3753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:25" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:25" ht="27" customHeight="1">
       <c r="B4" s="31" t="s">
         <v>6</v>
       </c>
@@ -3717,24 +3763,24 @@
       <c r="D4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="123" t="s">
+      <c r="E4" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="124"/>
-      <c r="G4" s="125" t="s">
+      <c r="F4" s="135"/>
+      <c r="G4" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="126"/>
-      <c r="I4" s="127" t="s">
+      <c r="H4" s="105"/>
+      <c r="I4" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="128"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="159"/>
-      <c r="M4" s="159"/>
-      <c r="N4" s="159"/>
-      <c r="O4" s="159"/>
-      <c r="P4" s="128"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="107"/>
       <c r="Q4" s="5" t="s">
         <v>12</v>
       </c>
@@ -3742,34 +3788,34 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:25" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="104" t="s">
+    <row r="5" spans="2:25" ht="30.75" customHeight="1" thickBot="1">
+      <c r="B5" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="105"/>
-      <c r="D5" s="106" t="s">
+      <c r="C5" s="109"/>
+      <c r="D5" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="106"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
       <c r="I5" s="41" t="s">
         <v>16</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="141" t="s">
+      <c r="K5" s="136" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="142"/>
+      <c r="L5" s="137"/>
       <c r="M5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="143"/>
-      <c r="O5" s="144"/>
-      <c r="P5" s="145"/>
+      <c r="N5" s="138"/>
+      <c r="O5" s="139"/>
+      <c r="P5" s="140"/>
       <c r="Q5" s="25" t="s">
         <v>19</v>
       </c>
@@ -3777,40 +3823,40 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:25" ht="29.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:25" ht="29.5" customHeight="1" thickBot="1">
       <c r="B6" s="33" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="139" t="s">
+      <c r="D6" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="140"/>
-      <c r="F6" s="146" t="s">
+      <c r="E6" s="133"/>
+      <c r="F6" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="147"/>
-      <c r="H6" s="147"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="142"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="148" t="s">
+      <c r="J6" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="149"/>
-      <c r="L6" s="150"/>
-      <c r="M6" s="151" t="s">
+      <c r="K6" s="144"/>
+      <c r="L6" s="145"/>
+      <c r="M6" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="152"/>
-      <c r="O6" s="156" t="s">
+      <c r="N6" s="147"/>
+      <c r="O6" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="157"/>
-      <c r="Q6" s="157"/>
-      <c r="R6" s="158"/>
-    </row>
-    <row r="7" spans="2:25" s="7" customFormat="1" ht="52" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="P6" s="102"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="103"/>
+    </row>
+    <row r="7" spans="2:25" s="7" customFormat="1" ht="45.5" thickBot="1">
       <c r="B7" s="34" t="s">
         <v>27</v>
       </c>
@@ -3863,7 +3909,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="2:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:25" s="2" customFormat="1" ht="15.5">
       <c r="B8" s="36">
         <v>1</v>
       </c>
@@ -3890,7 +3936,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:25" s="2" customFormat="1" ht="15.5">
       <c r="B9" s="36">
         <v>2</v>
       </c>
@@ -3918,7 +3964,7 @@
       </c>
       <c r="Y9" s="26"/>
     </row>
-    <row r="10" spans="2:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:25" s="2" customFormat="1" ht="15.5">
       <c r="B10" s="36">
         <v>3</v>
       </c>
@@ -3945,7 +3991,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:25" s="2" customFormat="1" ht="15.5">
       <c r="B11" s="36">
         <v>4</v>
       </c>
@@ -3972,7 +4018,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:25" s="2" customFormat="1" ht="15.5">
       <c r="B12" s="36">
         <v>5</v>
       </c>
@@ -3999,7 +4045,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:25" s="2" customFormat="1" ht="15.5">
       <c r="B13" s="36">
         <v>6</v>
       </c>
@@ -4026,7 +4072,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:25" s="2" customFormat="1" ht="15.5">
       <c r="B14" s="36">
         <v>7</v>
       </c>
@@ -4053,7 +4099,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="2:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:25" s="2" customFormat="1" ht="15.5">
       <c r="B15" s="36">
         <v>8</v>
       </c>
@@ -4080,7 +4126,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="2:25" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:25" s="2" customFormat="1" ht="15.5">
       <c r="B16" s="36">
         <v>9</v>
       </c>
@@ -4107,7 +4153,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B17" s="36">
         <v>10</v>
       </c>
@@ -4134,7 +4180,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B18" s="36">
         <v>11</v>
       </c>
@@ -4161,7 +4207,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B19" s="36">
         <v>12</v>
       </c>
@@ -4188,7 +4234,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B20" s="36">
         <v>13</v>
       </c>
@@ -4215,7 +4261,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B21" s="36">
         <v>14</v>
       </c>
@@ -4242,7 +4288,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B22" s="36">
         <v>15</v>
       </c>
@@ -4269,7 +4315,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B23" s="36">
         <v>16</v>
       </c>
@@ -4296,7 +4342,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B24" s="36">
         <v>17</v>
       </c>
@@ -4323,7 +4369,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B25" s="36">
         <v>18</v>
       </c>
@@ -4350,7 +4396,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B26" s="36">
         <v>19</v>
       </c>
@@ -4377,7 +4423,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:18" s="2" customFormat="1" ht="15.5">
       <c r="B27" s="36">
         <v>20</v>
       </c>
@@ -4404,102 +4450,94 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:18" s="2" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:18" s="2" customFormat="1" ht="108.75" customHeight="1">
       <c r="B28" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="96" t="s">
+      <c r="C28" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="97"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="97"/>
-      <c r="H28" s="97"/>
-      <c r="I28" s="97"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="97"/>
-      <c r="L28" s="97"/>
-      <c r="M28" s="97"/>
-      <c r="N28" s="97"/>
-      <c r="O28" s="97"/>
-      <c r="P28" s="97"/>
-      <c r="Q28" s="97"/>
-      <c r="R28" s="98"/>
-    </row>
-    <row r="29" spans="2:18" s="2" customFormat="1" ht="38.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D28" s="123"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="123"/>
+      <c r="G28" s="123"/>
+      <c r="H28" s="123"/>
+      <c r="I28" s="123"/>
+      <c r="J28" s="123"/>
+      <c r="K28" s="123"/>
+      <c r="L28" s="123"/>
+      <c r="M28" s="123"/>
+      <c r="N28" s="123"/>
+      <c r="O28" s="123"/>
+      <c r="P28" s="123"/>
+      <c r="Q28" s="123"/>
+      <c r="R28" s="124"/>
+    </row>
+    <row r="29" spans="2:18" s="2" customFormat="1" ht="38.5" customHeight="1">
       <c r="B29" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="136" t="s">
+      <c r="C29" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="137"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="137"/>
-      <c r="I29" s="137"/>
-      <c r="J29" s="137"/>
-      <c r="K29" s="137"/>
-      <c r="L29" s="137"/>
-      <c r="M29" s="137"/>
-      <c r="N29" s="137"/>
-      <c r="O29" s="137"/>
-      <c r="P29" s="137"/>
-      <c r="Q29" s="137"/>
-      <c r="R29" s="138"/>
-    </row>
-    <row r="30" spans="2:18" s="6" customFormat="1" ht="163" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="160" t="s">
+      <c r="D29" s="126"/>
+      <c r="E29" s="126"/>
+      <c r="F29" s="126"/>
+      <c r="G29" s="126"/>
+      <c r="H29" s="126"/>
+      <c r="I29" s="126"/>
+      <c r="J29" s="126"/>
+      <c r="K29" s="126"/>
+      <c r="L29" s="126"/>
+      <c r="M29" s="126"/>
+      <c r="N29" s="126"/>
+      <c r="O29" s="126"/>
+      <c r="P29" s="126"/>
+      <c r="Q29" s="126"/>
+      <c r="R29" s="127"/>
+    </row>
+    <row r="30" spans="2:18" s="6" customFormat="1" ht="163" customHeight="1">
+      <c r="B30" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="161"/>
-      <c r="D30" s="161"/>
-      <c r="E30" s="161"/>
-      <c r="F30" s="161"/>
-      <c r="G30" s="161"/>
-      <c r="H30" s="161"/>
-      <c r="I30" s="161"/>
-      <c r="J30" s="161"/>
-      <c r="K30" s="161"/>
-      <c r="L30" s="161"/>
-      <c r="M30" s="161"/>
-      <c r="N30" s="161"/>
-      <c r="O30" s="161"/>
-      <c r="P30" s="161"/>
-      <c r="Q30" s="161"/>
-      <c r="R30" s="162"/>
-    </row>
-    <row r="31" spans="2:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="153"/>
-      <c r="C31" s="154"/>
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="154"/>
-      <c r="H31" s="154"/>
-      <c r="I31" s="154"/>
-      <c r="J31" s="154"/>
-      <c r="K31" s="154"/>
-      <c r="L31" s="154"/>
-      <c r="M31" s="154"/>
-      <c r="N31" s="154"/>
-      <c r="O31" s="154"/>
-      <c r="P31" s="154"/>
-      <c r="Q31" s="154"/>
-      <c r="R31" s="155"/>
+      <c r="C30" s="113"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="113"/>
+      <c r="M30" s="113"/>
+      <c r="N30" s="113"/>
+      <c r="O30" s="113"/>
+      <c r="P30" s="113"/>
+      <c r="Q30" s="113"/>
+      <c r="R30" s="114"/>
+    </row>
+    <row r="31" spans="2:18" ht="24" customHeight="1" thickBot="1">
+      <c r="B31" s="98"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="99"/>
+      <c r="H31" s="99"/>
+      <c r="I31" s="99"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="99"/>
+      <c r="M31" s="99"/>
+      <c r="N31" s="99"/>
+      <c r="O31" s="99"/>
+      <c r="P31" s="99"/>
+      <c r="Q31" s="99"/>
+      <c r="R31" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B31:R31"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="K4:P4"/>
-    <mergeCell ref="B30:R30"/>
     <mergeCell ref="D2:P2"/>
     <mergeCell ref="D3:P3"/>
     <mergeCell ref="C28:R28"/>
@@ -4512,6 +4550,14 @@
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="M6:N6"/>
+    <mergeCell ref="B31:R31"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="K4:P4"/>
+    <mergeCell ref="B30:R30"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="C8:C27">
@@ -4582,9 +4628,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314B0786-27B5-46FD-B0B7-2C89A48834F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:W94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="1" bestFit="1" customWidth="1"/>
@@ -4605,25 +4651,23 @@
     <col min="19" max="16384" width="7.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:23" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="113" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="117" t="s">
+    <row r="1" spans="2:23" ht="14.5" thickBot="1"/>
+    <row r="2" spans="2:23" ht="29.25" customHeight="1">
+      <c r="B2" s="128"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="148" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
-      <c r="N2" s="119"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="150"/>
       <c r="O2" s="42" t="s">
         <v>1</v>
       </c>
@@ -4632,22 +4676,22 @@
       </c>
       <c r="Q2" s="44"/>
     </row>
-    <row r="3" spans="2:23" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="115"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="120" t="s">
+    <row r="3" spans="2:23" ht="30.75" customHeight="1">
+      <c r="B3" s="130"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="151" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="122"/>
+      <c r="E3" s="152"/>
+      <c r="F3" s="152"/>
+      <c r="G3" s="152"/>
+      <c r="H3" s="152"/>
+      <c r="I3" s="152"/>
+      <c r="J3" s="152"/>
+      <c r="K3" s="152"/>
+      <c r="L3" s="152"/>
+      <c r="M3" s="152"/>
+      <c r="N3" s="153"/>
       <c r="O3" s="45" t="s">
         <v>4</v>
       </c>
@@ -4656,7 +4700,7 @@
       </c>
       <c r="Q3" s="44"/>
     </row>
-    <row r="4" spans="2:23" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:23" s="2" customFormat="1" ht="33.75" customHeight="1">
       <c r="B4" s="31" t="s">
         <v>6</v>
       </c>
@@ -4666,18 +4710,18 @@
       <c r="D4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="123" t="s">
+      <c r="E4" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="124"/>
-      <c r="G4" s="125" t="s">
+      <c r="F4" s="135"/>
+      <c r="G4" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="126"/>
-      <c r="I4" s="127" t="s">
+      <c r="H4" s="105"/>
+      <c r="I4" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="128"/>
+      <c r="J4" s="107"/>
       <c r="K4" s="47"/>
       <c r="L4" s="48"/>
       <c r="M4" s="48"/>
@@ -4690,18 +4734,18 @@
       </c>
       <c r="Q4" s="49"/>
     </row>
-    <row r="5" spans="2:23" s="54" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="104" t="s">
+    <row r="5" spans="2:23" s="54" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
+      <c r="B5" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="105"/>
-      <c r="D5" s="106" t="s">
+      <c r="C5" s="109"/>
+      <c r="D5" s="110" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="106"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
       <c r="I5" s="41" t="s">
         <v>16</v>
       </c>
@@ -4723,38 +4767,38 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="2:23" s="2" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:23" s="2" customFormat="1" ht="32.25" customHeight="1">
       <c r="B6" s="33" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="107" t="s">
+      <c r="D6" s="154" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="108"/>
-      <c r="F6" s="109" t="s">
+      <c r="E6" s="155"/>
+      <c r="F6" s="156" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
       <c r="I6" s="55"/>
-      <c r="J6" s="111" t="s">
+      <c r="J6" s="158" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="112"/>
-      <c r="L6" s="102" t="s">
+      <c r="K6" s="159"/>
+      <c r="L6" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="103"/>
-      <c r="N6" s="99" t="s">
+      <c r="M6" s="170"/>
+      <c r="N6" s="166" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="100"/>
-      <c r="P6" s="101"/>
-    </row>
-    <row r="7" spans="2:23" s="7" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O6" s="167"/>
+      <c r="P6" s="168"/>
+    </row>
+    <row r="7" spans="2:23" s="7" customFormat="1" ht="59.25" customHeight="1">
       <c r="B7" s="34" t="s">
         <v>27</v>
       </c>
@@ -4801,7 +4845,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="2:23" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:23" s="2" customFormat="1" ht="17.25" customHeight="1">
       <c r="B8" s="74">
         <v>1</v>
       </c>
@@ -4850,7 +4894,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="9" spans="2:23" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:23" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="B9" s="75">
         <v>2</v>
       </c>
@@ -4900,7 +4944,7 @@
       </c>
       <c r="W9" s="26"/>
     </row>
-    <row r="10" spans="2:23" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:23" s="2" customFormat="1" ht="15.5">
       <c r="B10" s="75">
         <v>3</v>
       </c>
@@ -4949,7 +4993,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="11" spans="2:23" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:23" s="2" customFormat="1" ht="15.5">
       <c r="B11" s="75">
         <v>4</v>
       </c>
@@ -4998,7 +5042,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="12" spans="2:23" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:23" s="2" customFormat="1" ht="15.75" customHeight="1">
       <c r="B12" s="75">
         <v>5</v>
       </c>
@@ -5047,7 +5091,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="13" spans="2:23" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:23" s="2" customFormat="1" ht="15.5">
       <c r="B13" s="74">
         <v>6</v>
       </c>
@@ -5096,7 +5140,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="14" spans="2:23" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:23" s="2" customFormat="1" ht="15.5">
       <c r="B14" s="75">
         <v>7</v>
       </c>
@@ -5145,7 +5189,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="15" spans="2:23" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:23" s="2" customFormat="1" ht="15.5">
       <c r="B15" s="75">
         <v>8</v>
       </c>
@@ -5194,7 +5238,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="16" spans="2:23" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:23" s="2" customFormat="1" ht="15.5">
       <c r="B16" s="74">
         <v>9</v>
       </c>
@@ -5243,7 +5287,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="17" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B17" s="75">
         <v>10</v>
       </c>
@@ -5292,7 +5336,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="18" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B18" s="75">
         <v>11</v>
       </c>
@@ -5341,7 +5385,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="19" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B19" s="74">
         <v>12</v>
       </c>
@@ -5390,7 +5434,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="20" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B20" s="75">
         <v>13</v>
       </c>
@@ -5439,7 +5483,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="21" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B21" s="75">
         <v>14</v>
       </c>
@@ -5488,7 +5532,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="22" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B22" s="74">
         <v>15</v>
       </c>
@@ -5537,7 +5581,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="23" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B23" s="75">
         <v>16</v>
       </c>
@@ -5586,7 +5630,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="24" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B24" s="75">
         <v>17</v>
       </c>
@@ -5635,7 +5679,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="25" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B25" s="74">
         <v>18</v>
       </c>
@@ -5684,7 +5728,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="26" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B26" s="75">
         <v>19</v>
       </c>
@@ -5733,7 +5777,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="27" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B27" s="75">
         <v>20</v>
       </c>
@@ -5782,7 +5826,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="28" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B28" s="74">
         <v>21</v>
       </c>
@@ -5831,7 +5875,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="29" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B29" s="75">
         <v>22</v>
       </c>
@@ -5880,7 +5924,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="30" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B30" s="75">
         <v>23</v>
       </c>
@@ -5929,7 +5973,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="31" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B31" s="74">
         <v>24</v>
       </c>
@@ -5978,7 +6022,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="32" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B32" s="75">
         <v>25</v>
       </c>
@@ -6027,7 +6071,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="33" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B33" s="75">
         <v>26</v>
       </c>
@@ -6076,7 +6120,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="34" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B34" s="74">
         <v>27</v>
       </c>
@@ -6125,7 +6169,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="35" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B35" s="75">
         <v>28</v>
       </c>
@@ -6174,7 +6218,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="36" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B36" s="75">
         <v>29</v>
       </c>
@@ -6223,7 +6267,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="37" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B37" s="74">
         <v>30</v>
       </c>
@@ -6272,7 +6316,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="38" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B38" s="75">
         <v>31</v>
       </c>
@@ -6321,7 +6365,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="39" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B39" s="75">
         <v>32</v>
       </c>
@@ -6370,7 +6414,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="40" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B40" s="74">
         <v>33</v>
       </c>
@@ -6419,7 +6463,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="41" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B41" s="75">
         <v>34</v>
       </c>
@@ -6468,7 +6512,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="42" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B42" s="75">
         <v>35</v>
       </c>
@@ -6517,7 +6561,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="43" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B43" s="74">
         <v>36</v>
       </c>
@@ -6566,7 +6610,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="44" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B44" s="75">
         <v>37</v>
       </c>
@@ -6615,7 +6659,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="45" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B45" s="75">
         <v>38</v>
       </c>
@@ -6664,7 +6708,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="46" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B46" s="74">
         <v>39</v>
       </c>
@@ -6713,7 +6757,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="47" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B47" s="75">
         <v>40</v>
       </c>
@@ -6762,7 +6806,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="48" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B48" s="75">
         <v>41</v>
       </c>
@@ -6811,7 +6855,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="49" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B49" s="74">
         <v>42</v>
       </c>
@@ -6860,7 +6904,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="50" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B50" s="75">
         <v>43</v>
       </c>
@@ -6909,7 +6953,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="51" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B51" s="75">
         <v>44</v>
       </c>
@@ -6958,7 +7002,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="52" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B52" s="74">
         <v>45</v>
       </c>
@@ -7007,7 +7051,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="53" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B53" s="75">
         <v>46</v>
       </c>
@@ -7056,7 +7100,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="54" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B54" s="75">
         <v>47</v>
       </c>
@@ -7105,7 +7149,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="55" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B55" s="74">
         <v>48</v>
       </c>
@@ -7154,7 +7198,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="56" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B56" s="75">
         <v>49</v>
       </c>
@@ -7203,7 +7247,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="57" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B57" s="75">
         <v>50</v>
       </c>
@@ -7252,7 +7296,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="58" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B58" s="74">
         <v>51</v>
       </c>
@@ -7301,7 +7345,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="59" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B59" s="75">
         <v>52</v>
       </c>
@@ -7350,7 +7394,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="60" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B60" s="75">
         <v>53</v>
       </c>
@@ -7399,7 +7443,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="61" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B61" s="74">
         <v>54</v>
       </c>
@@ -7448,7 +7492,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="62" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B62" s="75">
         <v>55</v>
       </c>
@@ -7497,7 +7541,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="63" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B63" s="75">
         <v>56</v>
       </c>
@@ -7546,7 +7590,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="64" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B64" s="74">
         <v>57</v>
       </c>
@@ -7595,7 +7639,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="65" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B65" s="75">
         <v>58</v>
       </c>
@@ -7644,7 +7688,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="66" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B66" s="75">
         <v>59</v>
       </c>
@@ -7693,7 +7737,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="67" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B67" s="74">
         <v>60</v>
       </c>
@@ -7742,7 +7786,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="68" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B68" s="75">
         <v>61</v>
       </c>
@@ -7791,7 +7835,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="69" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B69" s="75">
         <v>62</v>
       </c>
@@ -7840,7 +7884,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="70" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B70" s="74">
         <v>63</v>
       </c>
@@ -7889,7 +7933,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="71" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B71" s="75">
         <v>64</v>
       </c>
@@ -7938,7 +7982,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="72" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B72" s="75">
         <v>65</v>
       </c>
@@ -7987,7 +8031,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="73" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B73" s="74">
         <v>66</v>
       </c>
@@ -8036,7 +8080,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="74" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B74" s="75">
         <v>67</v>
       </c>
@@ -8085,7 +8129,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="75" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B75" s="75">
         <v>68</v>
       </c>
@@ -8134,7 +8178,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="76" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B76" s="74">
         <v>69</v>
       </c>
@@ -8183,7 +8227,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="77" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B77" s="75">
         <v>70</v>
       </c>
@@ -8232,7 +8276,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="78" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B78" s="75">
         <v>71</v>
       </c>
@@ -8281,7 +8325,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="79" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B79" s="74">
         <v>72</v>
       </c>
@@ -8330,7 +8374,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="80" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B80" s="75">
         <v>73</v>
       </c>
@@ -8379,7 +8423,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="81" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B81" s="75">
         <v>74</v>
       </c>
@@ -8428,7 +8472,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="82" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B82" s="74">
         <v>75</v>
       </c>
@@ -8477,7 +8521,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="83" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B83" s="75">
         <v>76</v>
       </c>
@@ -8526,7 +8570,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="84" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B84" s="75">
         <v>77</v>
       </c>
@@ -8575,7 +8619,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="85" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B85" s="74">
         <v>78</v>
       </c>
@@ -8624,7 +8668,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="86" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B86" s="75">
         <v>79</v>
       </c>
@@ -8673,7 +8717,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="87" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B87" s="75">
         <v>80</v>
       </c>
@@ -8722,7 +8766,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="88" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B88" s="74">
         <v>81</v>
       </c>
@@ -8771,7 +8815,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="89" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B89" s="75">
         <v>82</v>
       </c>
@@ -8820,7 +8864,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="90" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B90" s="75">
         <v>83</v>
       </c>
@@ -8869,7 +8913,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="91" spans="2:16" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:16" s="2" customFormat="1" ht="15.5">
       <c r="B91" s="74">
         <v>84</v>
       </c>
@@ -8918,81 +8962,81 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="92" spans="2:16" s="2" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:16" s="2" customFormat="1" ht="37" customHeight="1">
       <c r="B92" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C92" s="96" t="s">
+      <c r="C92" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D92" s="97"/>
-      <c r="E92" s="97"/>
-      <c r="F92" s="97"/>
-      <c r="G92" s="97"/>
-      <c r="H92" s="97"/>
-      <c r="I92" s="97"/>
-      <c r="J92" s="97"/>
-      <c r="K92" s="97"/>
-      <c r="L92" s="97"/>
-      <c r="M92" s="97"/>
-      <c r="N92" s="97"/>
-      <c r="O92" s="97"/>
-      <c r="P92" s="98"/>
-    </row>
-    <row r="93" spans="2:16" s="6" customFormat="1" ht="170.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="93" t="s">
+      <c r="D92" s="123"/>
+      <c r="E92" s="123"/>
+      <c r="F92" s="123"/>
+      <c r="G92" s="123"/>
+      <c r="H92" s="123"/>
+      <c r="I92" s="123"/>
+      <c r="J92" s="123"/>
+      <c r="K92" s="123"/>
+      <c r="L92" s="123"/>
+      <c r="M92" s="123"/>
+      <c r="N92" s="123"/>
+      <c r="O92" s="123"/>
+      <c r="P92" s="124"/>
+    </row>
+    <row r="93" spans="2:16" s="6" customFormat="1" ht="170.25" customHeight="1">
+      <c r="B93" s="163" t="s">
         <v>137</v>
       </c>
-      <c r="C93" s="94"/>
-      <c r="D93" s="94"/>
-      <c r="E93" s="94"/>
-      <c r="F93" s="94"/>
-      <c r="G93" s="94"/>
-      <c r="H93" s="94"/>
-      <c r="I93" s="94"/>
-      <c r="J93" s="94"/>
-      <c r="K93" s="94"/>
-      <c r="L93" s="94"/>
-      <c r="M93" s="94"/>
-      <c r="N93" s="94"/>
-      <c r="O93" s="94"/>
-      <c r="P93" s="95"/>
-    </row>
-    <row r="94" spans="2:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B94" s="90"/>
-      <c r="C94" s="91"/>
-      <c r="D94" s="91"/>
-      <c r="E94" s="91"/>
-      <c r="F94" s="91"/>
-      <c r="G94" s="91"/>
-      <c r="H94" s="91"/>
-      <c r="I94" s="91"/>
-      <c r="J94" s="91"/>
-      <c r="K94" s="91"/>
-      <c r="L94" s="91"/>
-      <c r="M94" s="91"/>
-      <c r="N94" s="91"/>
-      <c r="O94" s="91"/>
-      <c r="P94" s="92"/>
+      <c r="C93" s="164"/>
+      <c r="D93" s="164"/>
+      <c r="E93" s="164"/>
+      <c r="F93" s="164"/>
+      <c r="G93" s="164"/>
+      <c r="H93" s="164"/>
+      <c r="I93" s="164"/>
+      <c r="J93" s="164"/>
+      <c r="K93" s="164"/>
+      <c r="L93" s="164"/>
+      <c r="M93" s="164"/>
+      <c r="N93" s="164"/>
+      <c r="O93" s="164"/>
+      <c r="P93" s="165"/>
+    </row>
+    <row r="94" spans="2:16" ht="20.25" customHeight="1">
+      <c r="B94" s="160"/>
+      <c r="C94" s="161"/>
+      <c r="D94" s="161"/>
+      <c r="E94" s="161"/>
+      <c r="F94" s="161"/>
+      <c r="G94" s="161"/>
+      <c r="H94" s="161"/>
+      <c r="I94" s="161"/>
+      <c r="J94" s="161"/>
+      <c r="K94" s="161"/>
+      <c r="L94" s="161"/>
+      <c r="M94" s="161"/>
+      <c r="N94" s="161"/>
+      <c r="O94" s="161"/>
+      <c r="P94" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B94:P94"/>
+    <mergeCell ref="B93:P93"/>
+    <mergeCell ref="C92:P92"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="J6:K6"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:N2"/>
     <mergeCell ref="D3:N3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B94:P94"/>
-    <mergeCell ref="B93:P93"/>
-    <mergeCell ref="C92:P92"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="L6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="F8:F91">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
@@ -9013,13 +9057,14 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E0C347-98F7-464D-94A6-D06718C4916A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:R6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.33203125" customWidth="1"/>
@@ -9038,38 +9083,38 @@
     <col min="16" max="16" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" s="2" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" s="2" customFormat="1" ht="32.25" customHeight="1">
       <c r="B2" s="77" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="163" t="s">
+      <c r="D2" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="163"/>
-      <c r="F2" s="164" t="s">
+      <c r="E2" s="171"/>
+      <c r="F2" s="172" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
       <c r="I2" s="78"/>
-      <c r="J2" s="165" t="s">
+      <c r="J2" s="173" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="165"/>
-      <c r="L2" s="166" t="s">
+      <c r="K2" s="173"/>
+      <c r="L2" s="174" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="166"/>
-      <c r="N2" s="167" t="s">
+      <c r="M2" s="174"/>
+      <c r="N2" s="175" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="167"/>
-      <c r="P2" s="167"/>
-    </row>
-    <row r="3" spans="1:18" s="7" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O2" s="175"/>
+      <c r="P2" s="175"/>
+    </row>
+    <row r="3" spans="1:18" s="7" customFormat="1" ht="59.25" customHeight="1">
       <c r="B3" s="79" t="s">
         <v>27</v>
       </c>
@@ -9116,7 +9161,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="76" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" s="76" customFormat="1" ht="207" customHeight="1">
       <c r="B4" s="89"/>
       <c r="C4" s="89" t="s">
         <v>146</v>
@@ -9163,7 +9208,7 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
     </row>
-    <row r="5" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="15.5">
       <c r="O5" t="s">
         <v>145</v>
       </c>
@@ -9173,7 +9218,7 @@
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
     </row>
-    <row r="6" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="15.5">
       <c r="A6" t="s">
         <v>138</v>
       </c>
@@ -9200,429 +9245,429 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50DE659F-86D3-9240-9429-2AEBD1A0E846}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="126.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5" style="171" customWidth="1"/>
-    <col min="4" max="4" width="41.1640625" style="171" customWidth="1"/>
+    <col min="3" max="3" width="33.5" style="93" customWidth="1"/>
+    <col min="4" max="4" width="41.1640625" style="93" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="168" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="90" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="168" t="s">
+      <c r="B1" s="90" t="s">
         <v>190</v>
       </c>
-      <c r="C1" s="170" t="s">
+      <c r="C1" s="92" t="s">
         <v>191</v>
       </c>
-      <c r="D1" s="170" t="s">
+      <c r="D1" s="92" t="s">
         <v>192</v>
       </c>
-      <c r="E1" s="169"/>
-    </row>
-    <row r="2" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A2" s="172">
+      <c r="E1" s="91"/>
+    </row>
+    <row r="2" spans="1:5" ht="56">
+      <c r="A2" s="94">
         <v>1</v>
       </c>
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="94" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="178" t="s">
+      <c r="C2" s="97" t="s">
         <v>193</v>
       </c>
       <c r="D2" s="89"/>
-      <c r="E2" s="169"/>
-    </row>
-    <row r="3" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A3" s="172">
+      <c r="E2" s="91"/>
+    </row>
+    <row r="3" spans="1:5" ht="56">
+      <c r="A3" s="94">
         <v>2</v>
       </c>
-      <c r="B3" s="172" t="s">
+      <c r="B3" s="94" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="173" t="s">
+      <c r="C3" s="95" t="s">
         <v>194</v>
       </c>
       <c r="D3" s="89"/>
-      <c r="E3" s="169"/>
-    </row>
-    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="172">
+      <c r="E3" s="91"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.5">
+      <c r="A4" s="94">
         <v>3</v>
       </c>
-      <c r="B4" s="172" t="s">
+      <c r="B4" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="177"/>
+      <c r="C4" s="96"/>
       <c r="D4" s="89"/>
-      <c r="E4" s="169"/>
-    </row>
-    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="172">
+      <c r="E4" s="91"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.5">
+      <c r="A5" s="94">
         <v>4</v>
       </c>
-      <c r="B5" s="172" t="s">
+      <c r="B5" s="94" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="177"/>
+      <c r="C5" s="96"/>
       <c r="D5" s="89"/>
-      <c r="E5" s="169"/>
-    </row>
-    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="172">
+      <c r="E5" s="91"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.5">
+      <c r="A6" s="94">
         <v>5</v>
       </c>
-      <c r="B6" s="172" t="s">
+      <c r="B6" s="94" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="177"/>
+      <c r="C6" s="96"/>
       <c r="D6" s="89"/>
-      <c r="E6" s="169"/>
-    </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="172"/>
-      <c r="B7" s="172" t="s">
+      <c r="E6" s="91"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.5">
+      <c r="A7" s="94"/>
+      <c r="B7" s="94" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="177"/>
+      <c r="C7" s="96"/>
       <c r="D7" s="89"/>
-      <c r="E7" s="169"/>
-    </row>
-    <row r="8" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="172">
+      <c r="E7" s="91"/>
+    </row>
+    <row r="8" spans="1:5" ht="56">
+      <c r="A8" s="94">
         <v>6</v>
       </c>
-      <c r="B8" s="172" t="s">
+      <c r="B8" s="94" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="173" t="s">
+      <c r="C8" s="95" t="s">
         <v>194</v>
       </c>
       <c r="D8" s="89"/>
-      <c r="E8" s="169"/>
-    </row>
-    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="172">
+      <c r="E8" s="91"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="94">
         <v>7</v>
       </c>
-      <c r="B9" s="172" t="s">
+      <c r="B9" s="94" t="s">
         <v>182</v>
       </c>
       <c r="C9" s="89" t="s">
         <v>195</v>
       </c>
       <c r="D9" s="89"/>
-      <c r="E9" s="169"/>
-    </row>
-    <row r="10" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A10" s="172">
+      <c r="E9" s="91"/>
+    </row>
+    <row r="10" spans="1:5" ht="56">
+      <c r="A10" s="94">
         <v>8</v>
       </c>
-      <c r="B10" s="172" t="s">
+      <c r="B10" s="94" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="178" t="s">
+      <c r="C10" s="97" t="s">
         <v>193</v>
       </c>
       <c r="D10" s="89"/>
-      <c r="E10" s="169"/>
-    </row>
-    <row r="11" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A11" s="172">
+      <c r="E10" s="91"/>
+    </row>
+    <row r="11" spans="1:5" ht="56">
+      <c r="A11" s="94">
         <v>9</v>
       </c>
-      <c r="B11" s="172" t="s">
+      <c r="B11" s="94" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="173" t="s">
+      <c r="C11" s="95" t="s">
         <v>194</v>
       </c>
       <c r="D11" s="89"/>
-      <c r="E11" s="169"/>
-    </row>
-    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="172">
+      <c r="E11" s="91"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.5">
+      <c r="A12" s="94">
         <v>10</v>
       </c>
-      <c r="B12" s="172" t="s">
+      <c r="B12" s="94" t="s">
         <v>179</v>
       </c>
-      <c r="C12" s="177"/>
+      <c r="C12" s="96"/>
       <c r="D12" s="89"/>
-      <c r="E12" s="169"/>
-    </row>
-    <row r="13" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="172">
+      <c r="E12" s="91"/>
+    </row>
+    <row r="13" spans="1:5" ht="56">
+      <c r="A13" s="94">
         <v>11</v>
       </c>
-      <c r="B13" s="172" t="s">
+      <c r="B13" s="94" t="s">
         <v>178</v>
       </c>
-      <c r="C13" s="173" t="s">
+      <c r="C13" s="95" t="s">
         <v>194</v>
       </c>
       <c r="D13" s="89"/>
-      <c r="E13" s="169"/>
-    </row>
-    <row r="14" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A14" s="172">
+      <c r="E13" s="91"/>
+    </row>
+    <row r="14" spans="1:5" ht="56">
+      <c r="A14" s="94">
         <v>12</v>
       </c>
-      <c r="B14" s="172" t="s">
+      <c r="B14" s="94" t="s">
         <v>177</v>
       </c>
-      <c r="C14" s="178" t="s">
+      <c r="C14" s="97" t="s">
         <v>193</v>
       </c>
       <c r="D14" s="89"/>
-      <c r="E14" s="169"/>
-    </row>
-    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="172">
+      <c r="E14" s="91"/>
+    </row>
+    <row r="15" spans="1:5" ht="15.5">
+      <c r="A15" s="94">
         <v>13</v>
       </c>
-      <c r="B15" s="172" t="s">
+      <c r="B15" s="94" t="s">
         <v>176</v>
       </c>
-      <c r="C15" s="177"/>
+      <c r="C15" s="96"/>
       <c r="D15" s="89"/>
-      <c r="E15" s="169"/>
-    </row>
-    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="172">
+      <c r="E15" s="91"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.5">
+      <c r="A16" s="94">
         <v>14</v>
       </c>
-      <c r="B16" s="172" t="s">
+      <c r="B16" s="94" t="s">
         <v>175</v>
       </c>
-      <c r="C16" s="177"/>
+      <c r="C16" s="96"/>
       <c r="D16" s="89"/>
-      <c r="E16" s="169"/>
-    </row>
-    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="172">
+      <c r="E16" s="91"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.5">
+      <c r="A17" s="94">
         <v>15</v>
       </c>
-      <c r="B17" s="172" t="s">
+      <c r="B17" s="94" t="s">
         <v>174</v>
       </c>
-      <c r="C17" s="177"/>
+      <c r="C17" s="96"/>
       <c r="D17" s="89"/>
-      <c r="E17" s="169"/>
-    </row>
-    <row r="18" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A18" s="172">
+      <c r="E17" s="91"/>
+    </row>
+    <row r="18" spans="1:5" ht="56">
+      <c r="A18" s="94">
         <v>16</v>
       </c>
-      <c r="B18" s="172" t="s">
+      <c r="B18" s="94" t="s">
         <v>173</v>
       </c>
-      <c r="C18" s="178" t="s">
+      <c r="C18" s="97" t="s">
         <v>193</v>
       </c>
       <c r="D18" s="89"/>
-      <c r="E18" s="169"/>
-    </row>
-    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="172">
+      <c r="E18" s="91"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.5">
+      <c r="A19" s="94">
         <v>17</v>
       </c>
-      <c r="B19" s="172" t="s">
+      <c r="B19" s="94" t="s">
         <v>172</v>
       </c>
-      <c r="C19" s="177"/>
+      <c r="C19" s="96"/>
       <c r="D19" s="89"/>
-      <c r="E19" s="169"/>
-    </row>
-    <row r="20" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A20" s="172">
+      <c r="E19" s="91"/>
+    </row>
+    <row r="20" spans="1:5" ht="56">
+      <c r="A20" s="94">
         <v>18</v>
       </c>
-      <c r="B20" s="172" t="s">
+      <c r="B20" s="94" t="s">
         <v>171</v>
       </c>
-      <c r="C20" s="173" t="s">
+      <c r="C20" s="95" t="s">
         <v>194</v>
       </c>
       <c r="D20" s="89"/>
-      <c r="E20" s="169"/>
-    </row>
-    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="172">
+      <c r="E20" s="91"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.5">
+      <c r="A21" s="94">
         <v>19</v>
       </c>
-      <c r="B21" s="172" t="s">
+      <c r="B21" s="94" t="s">
         <v>170</v>
       </c>
-      <c r="C21" s="177"/>
+      <c r="C21" s="96"/>
       <c r="D21" s="89"/>
-      <c r="E21" s="169"/>
-    </row>
-    <row r="22" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="172">
+      <c r="E21" s="91"/>
+    </row>
+    <row r="22" spans="1:5" ht="48" customHeight="1">
+      <c r="A22" s="94">
         <v>20</v>
       </c>
-      <c r="B22" s="172" t="s">
+      <c r="B22" s="94" t="s">
         <v>169</v>
       </c>
       <c r="C22" s="179" t="s">
         <v>194</v>
       </c>
       <c r="D22" s="89"/>
-      <c r="E22" s="169"/>
-    </row>
-    <row r="23" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="172">
+      <c r="E22" s="91"/>
+    </row>
+    <row r="23" spans="1:5" ht="48" customHeight="1">
+      <c r="A23" s="94">
         <v>21</v>
       </c>
-      <c r="B23" s="172" t="s">
+      <c r="B23" s="94" t="s">
         <v>168</v>
       </c>
       <c r="C23" s="180"/>
       <c r="D23" s="89"/>
-      <c r="E23" s="169"/>
-    </row>
-    <row r="24" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A24" s="172">
+      <c r="E23" s="91"/>
+    </row>
+    <row r="24" spans="1:5" ht="56">
+      <c r="A24" s="94">
         <v>22</v>
       </c>
-      <c r="B24" s="172" t="s">
+      <c r="B24" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="C24" s="178" t="s">
+      <c r="C24" s="97" t="s">
         <v>193</v>
       </c>
       <c r="D24" s="89"/>
-      <c r="E24" s="169"/>
-    </row>
-    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="172">
+      <c r="E24" s="91"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.5">
+      <c r="A25" s="94">
         <v>23</v>
       </c>
-      <c r="B25" s="172" t="s">
+      <c r="B25" s="94" t="s">
         <v>166</v>
       </c>
-      <c r="C25" s="177"/>
+      <c r="C25" s="96"/>
       <c r="D25" s="89"/>
-      <c r="E25" s="169"/>
-    </row>
-    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="172">
+      <c r="E25" s="91"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.5">
+      <c r="A26" s="94">
         <v>24</v>
       </c>
-      <c r="B26" s="172" t="s">
+      <c r="B26" s="94" t="s">
         <v>165</v>
       </c>
-      <c r="C26" s="177"/>
+      <c r="C26" s="96"/>
       <c r="D26" s="89"/>
-      <c r="E26" s="169"/>
-    </row>
-    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="172">
+      <c r="E26" s="91"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.5">
+      <c r="A27" s="94">
         <v>25</v>
       </c>
-      <c r="B27" s="172" t="s">
+      <c r="B27" s="94" t="s">
         <v>164</v>
       </c>
-      <c r="C27" s="177"/>
+      <c r="C27" s="96"/>
       <c r="D27" s="89"/>
-      <c r="E27" s="169"/>
-    </row>
-    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="172">
+      <c r="E27" s="91"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.5">
+      <c r="A28" s="94">
         <v>26</v>
       </c>
-      <c r="B28" s="172" t="s">
+      <c r="B28" s="94" t="s">
         <v>163</v>
       </c>
-      <c r="C28" s="177"/>
+      <c r="C28" s="96"/>
       <c r="D28" s="89"/>
-      <c r="E28" s="169"/>
-    </row>
-    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="172">
+      <c r="E28" s="91"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.5">
+      <c r="A29" s="94">
         <v>27</v>
       </c>
-      <c r="B29" s="172" t="s">
+      <c r="B29" s="94" t="s">
         <v>162</v>
       </c>
-      <c r="C29" s="177"/>
+      <c r="C29" s="96"/>
       <c r="D29" s="89"/>
-      <c r="E29" s="169"/>
-    </row>
-    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="172">
+      <c r="E29" s="91"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.5">
+      <c r="A30" s="94">
         <v>28</v>
       </c>
-      <c r="B30" s="172" t="s">
+      <c r="B30" s="94" t="s">
         <v>161</v>
       </c>
-      <c r="C30" s="177"/>
+      <c r="C30" s="96"/>
       <c r="D30" s="89"/>
-      <c r="E30" s="169"/>
-    </row>
-    <row r="31" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="172">
+      <c r="E30" s="91"/>
+    </row>
+    <row r="31" spans="1:5" ht="64" customHeight="1">
+      <c r="A31" s="94">
         <v>29</v>
       </c>
-      <c r="B31" s="172" t="s">
+      <c r="B31" s="94" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="174" t="s">
+      <c r="C31" s="176" t="s">
         <v>193</v>
       </c>
       <c r="D31" s="89"/>
-      <c r="E31" s="169"/>
-    </row>
-    <row r="32" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="172">
+      <c r="E31" s="91"/>
+    </row>
+    <row r="32" spans="1:5" ht="64" customHeight="1">
+      <c r="A32" s="94">
         <v>30</v>
       </c>
-      <c r="B32" s="172" t="s">
+      <c r="B32" s="94" t="s">
         <v>159</v>
       </c>
-      <c r="C32" s="175"/>
+      <c r="C32" s="177"/>
       <c r="D32" s="89"/>
-      <c r="E32" s="169"/>
-    </row>
-    <row r="33" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="172">
+      <c r="E32" s="91"/>
+    </row>
+    <row r="33" spans="1:5" ht="64" customHeight="1">
+      <c r="A33" s="94">
         <v>31</v>
       </c>
-      <c r="B33" s="172" t="s">
+      <c r="B33" s="94" t="s">
         <v>158</v>
       </c>
-      <c r="C33" s="176"/>
+      <c r="C33" s="178"/>
       <c r="D33" s="89"/>
-      <c r="E33" s="169"/>
-    </row>
-    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="172">
+      <c r="E33" s="91"/>
+    </row>
+    <row r="34" spans="1:5" ht="15.5">
+      <c r="A34" s="94">
         <v>32</v>
       </c>
-      <c r="B34" s="172" t="s">
+      <c r="B34" s="94" t="s">
         <v>157</v>
       </c>
-      <c r="C34" s="177"/>
+      <c r="C34" s="96"/>
       <c r="D34" s="89"/>
-      <c r="E34" s="169"/>
-    </row>
-    <row r="35" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A35" s="172">
+      <c r="E34" s="91"/>
+    </row>
+    <row r="35" spans="1:5" ht="56">
+      <c r="A35" s="94">
         <v>33</v>
       </c>
-      <c r="B35" s="172" t="s">
+      <c r="B35" s="94" t="s">
         <v>156</v>
       </c>
-      <c r="C35" s="173" t="s">
+      <c r="C35" s="95" t="s">
         <v>194</v>
       </c>
       <c r="D35" s="89"/>
-      <c r="E35" s="169"/>
+      <c r="E35" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9634,6 +9679,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f05388af-b012-45d6-b4ee-8335fc1f514a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4392e905-69be-4d21-82f6-eaa7aa528137" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A71B55650E69AD46B0372B406DB091E1" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6699ae7dcb949edc488c90cabe01edec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f05388af-b012-45d6-b4ee-8335fc1f514a" xmlns:ns3="4392e905-69be-4d21-82f6-eaa7aa528137" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e78e10d48677905a91ddf459707bc36" ns2:_="" ns3:_="">
     <xsd:import namespace="f05388af-b012-45d6-b4ee-8335fc1f514a"/>
@@ -9828,17 +9884,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f05388af-b012-45d6-b4ee-8335fc1f514a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4392e905-69be-4d21-82f6-eaa7aa528137" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9849,6 +9894,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39BA0FCC-DD10-42DC-B4BF-71A4280A5B9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f05388af-b012-45d6-b4ee-8335fc1f514a"/>
+    <ds:schemaRef ds:uri="4392e905-69be-4d21-82f6-eaa7aa528137"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48409CA9-80C7-49D1-B112-3A3FD5183F80}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9867,17 +9923,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39BA0FCC-DD10-42DC-B4BF-71A4280A5B9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f05388af-b012-45d6-b4ee-8335fc1f514a"/>
-    <ds:schemaRef ds:uri="4392e905-69be-4d21-82f6-eaa7aa528137"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{647A3820-FDE5-42F9-9022-DC60484CB457}">
   <ds:schemaRefs>
